--- a/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-Next-80B-A3B-Instruct/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-Next-80B-A3B-Instruct/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>224</v>
+        <v>153</v>
       </c>
       <c r="D2">
-        <v>108</v>
+        <v>266</v>
       </c>
       <c r="E2">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="D3">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>78</v>
+        <v>17</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-Next-80B-A3B-Instruct/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-Next-80B-A3B-Instruct/simple/total_votes_file.xlsx
@@ -430,7 +430,7 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D2">
         <v>266</v>
@@ -439,7 +439,7 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D3">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="G3">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H3">
         <v>426</v>
